--- a/9_Movies_part1.xlsx
+++ b/9_Movies_part1.xlsx
@@ -1776,6 +1776,61 @@
           <t>G:\Archive\10091The Message 1977</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>The Message</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>The Message</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Moustapha Akkad</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Anthony Quinn, Irene Papas, Michael Ansara</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Biography, Drama, History</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Lebanon, Libya, Kuwait, Morocco, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Historical fresco recounting the life and times of the Prophet Mohammed, the last of the Abrahamic religion, in the sense that, according to Islam, he completed and sealed the monotheistic revelation made to Abraham.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODk0MDE2ZGYtYTljNS00Y2NlLWI4NTUtN2U4NTc2ODE2ZTA3XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1915,6 +1970,61 @@
           <t>G:\Archive\10094The Party 1968</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>The Party</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>The Party</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Blake Edwards</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Peter Sellers, Claudine Longet, Natalia Borisova</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Comedy, Romance</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A clerical mistake results in a bumbling Indian film star being invited to an exclusive Hollywood party instead of being fired.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjE4NjM3ZjYtMTllYy00YzIwLWE5YzYtZGM1ZDU3MGVjNzRmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2884,6 +2994,61 @@
           <t>G:\Archive\10107Man of the World (1931)</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Man of the World</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Man of the World</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Richard Wallace, Edward Goodman</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>William Powell, Carole Lombard, Wynne Gibson</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1931</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A young American girl visits Paris accompanied by her fiancee and her wealthy uncle. There she meets and is romanced by a worldly novelist; what she doesn't know is that he is a blackmailer who is using her to get to her uncle.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjFjNDUxYjctYzU2MC00ZThiLTkwY2YtZTQ2OWFjNGNkYTEwXkEyXkFqcGdeQXVyNTcwNjUwNzk@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3327,6 +3492,61 @@
           <t>G:\Archive\10113A Doll’s House 1973</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>A Dolls House</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>A Dolls House</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Jarryl Fordham</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Kat Bingham, Tony Knox, Joseph Martone, Sonia Sondheim</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A group of friends are brought to a haunted house to explore it for a doll that is being asked for by an online user for 25,000 but things turn out to be totally different then expected.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3936,6 +4156,61 @@
           <t>G:\Archive\10122Capricorn One 1977</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Capricorn One</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Capricorn One</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Peter Hyams</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Elliott Gould, James Brolin, Brenda Vaccaro</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>United States, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>When the first manned flight to Mars is deemed unsafe and scrubbed on the launch pad, anxious authorities must scramble to save face and retain their funding - and so an unthinkable plot to fake the mission is hatched.</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNTA1ODdlOTAtZGIyNi00N2U5LTg1ZDUtYTA2NzM4MDRlOTBhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4739,6 +5014,61 @@
           <t>G:\Archive\10133Jour de Fete 1949</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Un jour de fête</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Un jour de fête</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Philippe Arsenault</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Christine Beaulieu, Maïka Lafrenière, Arnaud Lemaire</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Short, Drama</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>On her birthday, a single mom tries to bring light in the lives of her two young children by inventing a car game where they conquer hidden corners of their village.</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNzY0OWM3OGYtMzRhYi00YjJkLThjY2QtZTQyOTI1MjdmNDkwXkEyXkFqcGdeQXVyMTA2NzA1NDYz._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6200,6 +6530,61 @@
           <t>G:\Archive\10155The Towering Inferno 1975</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>The Towering Inferno</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>The Towering Inferno</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>John Guillermin</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Paul Newman, Steve McQueen, William Holden</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Action, Drama, Thriller</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>At the opening party of a colossal San Francisco skyscraper, a massive fire breaks out due to careless building practices by the contractor, threatening to destroy the tower and everyone in it.</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTg0MmY2M2UtMjM4Zi00MDYyLTkwYjgtODZlZTQ1MmNjMDg5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6533,6 +6918,61 @@
           <t>G:\Archive\10161A Better Man (2017)</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>A Better Man</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>A Better Man</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Lawrence Jackman, Attiya Khan</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Attiya Khan</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Documentary</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Following a series of intimate conversations between a former couple who lived through two years of domestic abuse, A Better Man infuses new energy and possibility into the movement to end violence against women.</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMThkYTA2M2ItNmFmNC00MjMwLWI5MDUtNTI3MDdhYmQxYTIxXkEyXkFqcGdeQXVyNzM2ODIyNDM@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6893,6 +7333,61 @@
           <t>G:\Archive\10166An Old Lady (2019)</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>An Old Lady</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>An Old Lady</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Lim Seon-ae</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Ye Soo-jung, Gi Ju-bong, Joon-Kyung Kim</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Hyo-jeong, a 69-year-old woman, is raped by a male nurse aide. But few people, including the police, are willing to believe her words. Most people question whether that handsome young man really would have done so. The male nurse ...</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMThjNmIyYjItMjg4MS00ZjUzLWFiMDctYmMyNGQzYjBmMWIzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6949,6 +7444,61 @@
           <t>G:\Archive\10168Apollo 13 (1995)</t>
         </is>
       </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Apollo 13</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Apollo 13</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Ron Howard</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Tom Hanks, Bill Paxton, Kevin Bacon</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Adventure, Drama, History</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>NASA must devise a strategy to return Apollo 13 to Earth safely after the spacecraft undergoes massive internal damage putting the lives of the three astronauts on board in jeopardy.</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMGZmNGY1OTAtNjFkYS00MjcyLWFlZjUtYzEyMDllZGZhMzM3XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6977,6 +7527,61 @@
           <t>G:\Archive\10170Bigfoot Family (2020)</t>
         </is>
       </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bigfoot Family</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Bigfoot Family</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Jérémie Degruson, Ben Stassen</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Jules Medcraft, Kylian Trouillard, Alexis Victor</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Family</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Belgium, France</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Follow up to Son of Bigfoot: Father uses his new fame to fight against an Alaska oil company but when he disappears the son, the mother, a raccoon and a bear head North to rescue him.</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYWIxYWI0MDMtZjMwYS00OTUwLWI3ZTYtNTA3ZTAwY2U4MTk0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7005,6 +7610,61 @@
           <t>G:\Archive\10171Boss Level (2021)</t>
         </is>
       </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Boss Level</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Boss Level</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Joe Carnahan</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Frank Grillo, Mel Gibson, Naomi Watts</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Comedy</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>United States, Australia, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Trapped in a time loop that constantly repeats the day of his murder, a former special forces agent must unlock the mystery behind his untimely demise.</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNThlODU1ZjAtMWZkOS00NDc4LWE5ZjYtZTk1NzYwZTdjMmJhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7061,6 +7721,61 @@
           <t>G:\Archive\10173Call (2020)</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Better Call Saul</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Better Call Saul</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Bob Odenkirk, Rhea Seehorn, Jonathan Banks</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>2015–2022</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Albuquerque lawyer Jimmy McGill scrapes for clients and respect, but every win drags him closer to shady deals, dangerous players, and the alter ego Saul Goodman.</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNDdjNTEzMjMtYjM3Mi00NzQ3LWFlNWMtZjdmYWU3ZDkzMjk1XkEyXkFqcGc@._V1_QL75_UX380_CR0,0,380,562_.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7089,6 +7804,61 @@
           <t>G:\Archive\10174Chicago 10 (2007)</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Chicago 10</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Chicago 10</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Brett Morgen</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Jeffrey Wright, Nick Nolte, Roy Scheider</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Documentary, Animation, History</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Archival footage, animation, and music are used to look back at the eight anti-war protesters who were put on trial following the 1968 Democratic National Convention.</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTgzNjY5NDkxMF5BMl5BanBnXkFtZTcwNTE1OTc1MQ@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7117,6 +7887,61 @@
           <t>G:\Archive\10176Come Have Coffee with Us (1970)</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Come Have Coffee with Us</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Come Have Coffee with Us</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Alberto Lattuada</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Ugo Tognazzi, Francesca Romana Coluzzi, Milena Vukotic</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Comedy, Romance</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Emerenziano, a middle-aged tax inspector, is in search of a wealthy wife. He travels to Italy where he meets three sisters, who, though wealthy, are not by any stretch of the imagination young or beautiful. He decides to marry one...</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNzQ1MTQyOTkwOV5BMl5BanBnXkFtZTgwMzA1NzU2MDE@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7145,6 +7970,61 @@
           <t>G:\Archive\10177Cordelia (2019)</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Cordelia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Cordelia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Adrian Shergold</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Antonia Campbell-Hughes, Ryan Kelly, David Leon</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Drama, Horror, Thriller</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Following an incident in her past, Cordelia now lives with her twin sister, Caroline in their late father's basement flat.</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDdkZTI1MDQtNzMyMC00YzU3LTkxZDItMGI4NThlMmNiZTgyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7173,6 +8053,61 @@
           <t>G:\Archive\10178Dog’s Heart (1976)</t>
         </is>
       </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Devil Dogs Heart</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Devil Dogs Heart</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2023–</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>War</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7201,6 +8136,61 @@
           <t>G:\Archive\10179Digimon Adventure Last Evolution Kizuna (2020)</t>
         </is>
       </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Digimon Adventure: Last Evolution Kizuna</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Digimon Adventure: Last Evolution Kizuna</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Tomohisa Taguchi</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Natsuki Hanae, Yoshimasa Hosoya, Suzuko Mimori</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Animation, Action, Adventure</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>The team discovers that when they grow up, their relationship with their Digimon will come closer to an end. They realize that the more they fight, the faster their bond breaks and the time to choose is approaching fast.</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNGU1ZDNlZjAtOGVkYi00MWQ2LTlmMWUtYTNiYjg5MzcwMmMyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7229,6 +8219,61 @@
           <t>G:\Archive\10180Eye for an Eye (2008)</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Eye for an Eye</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Eye for an Eye</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>John Schlesinger</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Sally Field, Kiefer Sutherland, Ed Harris</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Crime, Drama, Thriller</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>When the courts fail to keep behind bars the man who raped and murdered her daughter, a woman seeks her own form of justice.</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYzg3MDc5ZWEtMTc3Ny00YWEzLTlmMTgtMjk3NGJjMmNjOTYyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7257,6 +8302,61 @@
           <t>G:\Archive\10181Falling (2020)</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Falling</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Falling</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Viggo Mortensen</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Viggo Mortensen, Lance Henriksen, Laura Linney</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>United Kingdom, Canada, United States</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>John Peterson lives with his partner Eric and their adopted daughter in Southern California. When he is visited by his aging father who is searching for a place to retire, their two very different worlds collide.</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDY2NWI3OWMtNTZmYi00ZjEzLWE4YWMtZWU0ZjBmYjdkNTc4XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7285,6 +8385,61 @@
           <t>G:\Archive\10182Goodfellas (1990)</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>GoodFellas</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>GoodFellas</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Martin Scorsese</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Robert De Niro, Ray Liotta, Joe Pesci</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Biography, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>The story of Henry Hill and his life in the mafia, covering his relationship with his wife Karen and his mob partners Jimmy Conway and Tommy DeVito.</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BN2E5NzI2ZGMtY2VjNi00YTRjLWI1MDUtZGY5OWU1MWJjZjRjXkEyXkFqcGc@._V1_QL75_UX380_CR0,3,380,562_.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7313,6 +8468,61 @@
           <t>G:\Archive\10184Hillbilly Elegy (2020)</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hillbilly Elegy</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Hillbilly Elegy</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Ron Howard</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Amy Adams, Glenn Close, Gabriel Basso</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Biography, Drama</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>An urgent phone call pulls a Yale Law student back to his Ohio hometown, where he reflects on three generations of family history and his own future.</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMWY0MThlOTgtNTg5ZS00ZTlkLTg2ZjAtMDE4YzAyNjExMjFkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7341,6 +8551,61 @@
           <t>G:\Archive\10185His House (2020)</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>His House</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>His House</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Remi Weekes</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Sope Dirisu, Wunmi Mosaku, Malaika Wakoli-Abigaba</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Drama, Horror, Thriller</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>United Kingdom, United States</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>A refugee couple makes a harrowing escape from war-torn South Sudan, but then they struggle to adjust to their new life in an English town that has an evil lurking beneath the surface.</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDBjNmYxMjctMjViNC00NmRlLWJkZWYtOTE2ZmY4ZDg3NmMyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7369,6 +8634,61 @@
           <t>G:\Archive\10186Honest Thief (2020)</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Honest Thief</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Honest Thief</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Mark Williams</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Liam Neeson, Kate Walsh, Jai Courtney</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Action, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Wanting to lead an honest life, a notorious bank robber turns himself in, only to be double-crossed by two ruthless FBI agents.</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNmY3Y2E0MzYtY2JjNy00MTNkLTllODYtZDIxY2ZkNWQ5MTRlXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7425,6 +8745,61 @@
           <t>G:\Archive\10188In Full Bloom (2019)</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>In Full Bloom</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>In Full Bloom</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Reza Ghassemi, Adam VillaSeñor</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Tyler Wood, Yusuke Ogasawara, Hiroyuki Watanabe</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Action, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>United States, Japan</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>In post-WWII Tokyo, Japan's undefeated Boxing Champion trains for his upcoming bout against the American challenger. Pitted amongst political tensions, the fighters' parallel journeys will test the very limits of human spirit.</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjc5YjQ2ODgtOWI3Zi00ZDA1LWJmMWYtMDNiMTU2ZDgyMmNmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7453,6 +8828,61 @@
           <t>G:\Archive\10189Wag the Dog 1997</t>
         </is>
       </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Wag the Dog</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Wag the Dog</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Barry Levinson</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Dustin Hoffman, Robert De Niro, Anne Heche</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Comedy, Drama</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Shortly before an election, a spin-doctor and a Hollywood producer join efforts to fabricate a war in order to cover up a Presidential sex scandal.</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNmEwNzk5ZTYtNGUzOC00ZThjLTk3NGYtMDQ5MzNiYzQ0ZTNkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7481,6 +8911,61 @@
           <t>G:\Archive\10190Joel (2018)</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Joel</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Carlos Sorin</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Victoria Almeida, Diego Gentile, Joel Noguera</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Unable to have kids of their own, Cecilia and Diego get a call from the adoption agency they registered to some time ago. The sudden arrival of Joel, a nine-year-old with a troubled history, will change the course of their lives.</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMmU0ODVjMjYtYWJlNy00Njk0LWExODUtNjZlZmFiNzkzZWUzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7509,6 +8994,61 @@
           <t>G:\Archive\10191Jungle (2017)</t>
         </is>
       </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Jungle</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Greg McLean</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Daniel Radcliffe, Thomas Kretschmann, Alex Russell</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Adventure, Biography, Drama</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Australia, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>A group of friends join a guide for a trek into the Bolivian jungle, searching for an Indian village. The men soon realize that the jungle is a difficult place to be.</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNDE4OTk4MTk0M15BMl5BanBnXkFtZTgwODQ4MTg0MzI@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7537,6 +9077,61 @@
           <t>G:\Archive\10192Kill Zone 2 (2015)</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Kill Zone 2</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Kill Zone 2</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Soi Cheang</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Tony Jaa, Jing Wu, Simon Yam</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Crime</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>China, Hong Kong</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>While undercover officer Kit is taken prisoner by the syndicate, he befriends his keeper and discovers an organ trafficking ring.</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODU2MjQ0ZTUtNTI2Ny00OTQ1LTk4YTktYzdjODc5MGMxY2Y5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7565,6 +9160,61 @@
           <t>G:\Archive\10193Loneliness of the Long Distance Runner (1962)</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>The Loneliness of the Long Distance Runner</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>The Loneliness of the Long Distance Runner</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Tony Richardson</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Michael Redgrave, Tom Courtenay, Avis Bunnage</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Drama, Sport</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>A young thief takes up long-distance running when he is sent to a borstal.</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDM3MDA5NGMtZDQ1Yi00ZjdhLTgxNzgtY2UyN2RmNzg2YmZjXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7593,6 +9243,61 @@
           <t>G:\Archive\10194Long Way North (2015)</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Long Way North</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Long Way North</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Rémi Chayé</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Christa Théret, Féodor Atkine, Thomas Sagols</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>France, Denmark, Belgium, United States</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>In 1882, a young Russian aristocrat goes on an epic adventure to find out what happened to her grandfather and save her family's reputation.</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjA4MTYwNzg2Ml5BMl5BanBnXkFtZTgwNjEzNTI4NzE@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7621,6 +9326,61 @@
           <t>G:\Archive\10195Made in Abyss Dawn of the Deep Soul (2020)</t>
         </is>
       </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Made in Abyss: Dawn of the Deep Soul</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Made in Abyss: Dawn of the Deep Soul</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Masayuki Kojima</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Miyu Tomita, Mariya Ise, Shiori Izawa</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Riko, Reg, and their new friend, Nanachi, continue their journey down the Abyss and arrive at the 5th layer. But in order for them to continue to the 6th layer, they must encounter the haunting figure of Nanachi's past: Bondrewd t...</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BY2QwZGNkYTktOGFlMi00MzgyLWFkMWMtMmFjZTUwZjFlMGI2XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7649,6 +9409,61 @@
           <t>G:\Archive\10196Mafia (1968)</t>
         </is>
       </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Mafia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Mafia</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Namit Das, Anindita Bose, Ishaa Saha</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Drama, Thriller</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>6.6</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Six friends who were extremely closely knit in their college days reunite for Tanya's bachelor party in Madhupur. However, all six of them are bound by a horrifying incident which had torn them apart for years. The reunion serves ...</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMzAxY2I3MDQtNGExNC00Y2Y5LThjYmEtZmU4ZDU5NmFlOWM5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7677,6 +9492,61 @@
           <t>G:\Archive\10197Mank (2020)</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Mank</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Mank</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>David Fincher</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Gary Oldman, Amanda Seyfried, Lily Collins</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Biography, Drama</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Scathing social critic and alcoholic screenwriter Herman J. Mankiewicz reflects on 1930s Hollywood as he races to finish the screenplay of Citizen Kane (1941).</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTA0NTI1ODYtZDVkMy00ZDU5LThiODgtYjEzYmNlZmUyYTg0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7844,6 +9714,61 @@
           <t>G:\Archive\10201Sound of Metal (2019)</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Sound of Metal</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sound of Metal</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Darius Marder</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Riz Ahmed, Olivia Cooke, Paul Raci</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Drama, Music</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>During a series of adrenaline-fueled gigs, itinerant punk-metal drummer Ruben begins to experience hearing loss. When a specialist tells him his condition will rapidly worsen, he thinks his music career - and with it his life - is...</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMWE5ZmYwNDEtYTYwMS00MTc0LTk2ZWItZTM1MjQ1ZDYzZGUzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7900,6 +9825,61 @@
           <t>G:\Archive\10203Tenet (2020)</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Tenet</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Tenet</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Christopher Nolan</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>John David Washington, Robert Pattinson, Elizabeth Debicki</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Action, Sci-Fi, Thriller</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>United Kingdom, United States</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Armed with only the word "Tenet," and fighting for the survival of the entire world, CIA operative, The Protagonist, journeys through a twilight world of international espionage on a global mission that unfolds beyond real time.</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNTIzNDIxMzktMzlkMi00MmUyLWFmMjQtZDgwMjBmOGJmNTI3XkEyXkFqcGc@._V1_QL75_UX380_CR0,0,380,562_.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7928,6 +9908,61 @@
           <t>G:\Archive\10204The Lark Farm 2007 (2007)</t>
         </is>
       </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>The Lark Farm</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>The Lark Farm</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Paolo Taviani, Vittorio Taviani</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Paz Vega, Moritz Bleibtreu, Alessandro Preziosi</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Drama, History</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Italy, Bulgaria, Spain, France, Germany</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>A stirring and stunning story of an aristocratic family who is unexpectedly swept into the ravages of World War I and a forbidden passion that may be the family's only hope.</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODk3Y2E5YTktY2JkOS00ZGEyLTliZGYtY2QzNzNjMjI0OGNkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7956,6 +9991,61 @@
           <t>G:\Archive\10205The Life Ahead (2020)</t>
         </is>
       </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>The Life Ahead</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>The Life Ahead</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Edoardo Ponti</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Sophia Loren, Ibrahima Gueye, Renato Carpentieri</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>In seaside Italy, a Holocaust survivor with a daycare business takes in a 12-year-old street kid who recently robbed her.</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMWM2YzA3YmUtN2EwMi00OTMxLWJmMDUtZGE1MWVkYzkzZWY0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -7984,6 +10074,61 @@
           <t>G:\Archive\10206The Master (2012)</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>The Master</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>The Master</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Paul Thomas Anderson</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Joaquin Phoenix, Philip Seymour Hoffman, Amy Adams</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>A Naval veteran arrives home from war unsettled and uncertain of his future - until he is tantalized by a cult and its charismatic leader.</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTQ2NjQ5MzMwMF5BMl5BanBnXkFtZTcwMjczNTAzOA@@._V1_QL75_UX380_CR0,0,380,562_.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8012,6 +10157,61 @@
           <t>G:\Archive\10207The Nest (2020)</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>The Nest</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>The Nest</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Sean Durkin</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Jude Law, Carrie Coon, Oona Roche</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Drama, Romance, Thriller</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>United Kingdom, Canada, United States</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Life for an entrepreneur and his American family begins to take a twisted turn after moving into an English country manor.</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDk0Nzk2NzEtMDA5OC00MjQ3LWJkYWEtYzY0YjFlY2UzYzk3XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8040,6 +10240,61 @@
           <t>G:\Archive\10209The SpongeBob Movie Sponge on the Run (2020)</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>The SpongeBob Movie: Sponge on the Run</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>The SpongeBob Movie: Sponge on the Run</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Tim Hill</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Tim Hill, Clancy Brown, Bill Fagerbakke</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Comedy</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>United States, Canada</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>After SpongeBob's beloved pet snail Gary is snail-napped, he and Patrick embark on an epic adventure to the Lost City of Atlantic City to bring Gary home.</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTBiZDQ2MWEtYzE1MC00YmMyLTg1NjUtNzE2YTZlMjI3MGUxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8068,6 +10323,61 @@
           <t>G:\Archive\10210The Walls of Malapaga (1949)</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>The Walls of Malapaga</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>The Walls of Malapaga</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>René Clément</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Jean Gabin, Isa Miranda, Vera Talchi</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Italy, France</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>A French fugitive arrives in Genoa, where he becomes entangled with an Italian woman and her daughter.</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDkyNzg0N2UtNjM0YS00YjBmLWEwNWQtZjk1ZTc2MTY0ZmM4XkEyXkFqcGdeQXVyOTI2MjI5MQ@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8096,6 +10406,61 @@
           <t>G:\Archive\10211The Wonderland (2019)</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>The Wonderland</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>The Wonderland</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Keiichi Hara</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Mayu Matsuoka, Anne Watanabe, Kumiko Asô</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Family</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>A girl without self-confidence meets a mysterious alchemist Hippocrates and his student Pipo who are on a mission to save the world. Together, they laid the groundwork for "Wonderland" and Akane is labeled as Wonderland's savior.</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZmNhYmQ5ZDUtNGRmMC00NTcyLWIyMmYtMTM1ZjM1OGI4ZTcwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8124,6 +10489,61 @@
           <t>G:\Archive\10212Vanina Vanini (1961)</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Vanina Vanini</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Vanina Vanini</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Helmut Schiemann</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Annekathrin Bürger, Reimar J. Baur, Erika Pelikowsky</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>1963</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>East Germany</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Set in 1820s during the early Risorgimento, when Italy was under Austrian control, it concerns the love affair of a young Roman princess and a revolutionary carbonaro. Vanina Vanini, the nineteen-year-old daughter of a Roman arist...</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8152,6 +10572,61 @@
           <t>G:\Archive\10221Chilsu and Mansu (1988)</t>
         </is>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Chilsu and Mansu</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Chilsu and Mansu</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Park Kwang-su</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Bae Jong-ok, Park Joong-hoon, Kang Shin-il</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Comedy, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>A painter quits his job and looks to an old acquaintance for work and a place to stay.</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOGEzZGJiNWMtZjE1OS00ZDdiLWEyZWMtZDY5MGE4ZGUxYTAzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8180,6 +10655,61 @@
           <t>G:\Archive\10222Csontvary (1980)</t>
         </is>
       </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Csontváry</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Csontváry</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Zoltán Huszárik</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Itschak Fintzi, István Holl, Andrea Drahota</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Tivadar Csontváry Kosztka the one-ideaed Hungarian painter was thought to be crazy by his peers, but he eventually became a significant artist.</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTgyNjc3NTctMjFmMi00MGM3LThhOTgtNDExZmUxNDk4Y2RlXkEyXkFqcGdeQXVyMzU0NzkwMDg@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8208,6 +10738,61 @@
           <t>G:\Archive\10223Eleven Samurai (1967)</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Eleven Samurai</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Eleven Samurai</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Eiichi Kudô</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Isao Natsuyagi, Kôtarô Satomi, Kôji Nanbara</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Adventure, Drama, History</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>The lord of the Oshi fief is killed by his trespassing neighbor, Nariatsu. But when the Oshi clan is blamed for the incident, eleven of their best warriors decide to trade their lives for justice.</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjI2NzhlMGYtNDYxNy00ZTc3LThkYzUtN2JjNGEwYzE0NjgxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8236,6 +10821,61 @@
           <t>G:\Archive\10224House of Wax (1953)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>House of Wax</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>House of Wax</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Jaume Collet-Serra</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Chad Michael Murray, Paris Hilton, Elisha Cuthbert</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Horror, Thriller</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Australia, United States</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>A group of teens are unwittingly stranded near a strange wax museum and soon must fight to survive and keep from becoming the next exhibit.</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNDA4Nzg1NjQ2NV5BMl5BanBnXkFtZTcwMDYwNTgyMQ@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8292,6 +10932,61 @@
           <t>G:\Archive\10226In This Our Life (1942)</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>In This Our Life</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>In This Our Life</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>John Huston, Raoul Walsh</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Bette Davis, Olivia de Havilland, George Brent</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>1942</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>The day before her wedding, a pampered young woman absconds with her sister's husband. Her sister begins seeing the woman's former fiancé.</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjA0ZDk1NDUtMjNiOS00MjZhLWExM2EtMTBjYjUzOTliM2ExXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -8320,6 +11015,61 @@
           <t>G:\Archive\10227Metello (1970)</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Metello</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Metello</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Mauro Bolognini</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Massimo Ranieri, Ottavia Piccolo, Frank Wolff</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Drama, History</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Struggling with life in 18th-century Italy, young Metello Salani is determined to change his situation for the better - but love, marriage and politics complicate things considerably...</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDE3YWRmNzMtMzY4OC00MjM3LTk3NDgtMWI0NjVhYzI5NjI5XkEyXkFqcGdeQXVyMzg1ODEwNQ@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8376,6 +11126,61 @@
           <t>G:\Archive\10229The Assassin (1961)</t>
         </is>
       </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>The Assassin</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>The Assassin</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Hsiao-Hsien Hou</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Shu Qi, Chang Chen, Yun Zhou</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Action, Drama, History</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Taiwan, Hong Kong, China</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>A female assassin receives a dangerous mission to kill a political leader in eighth-century China.</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNTczMTk3MjMyOV5BMl5BanBnXkFtZTgwMjA2Mjk4NjE@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -8404,6 +11209,61 @@
           <t>G:\Archive\10230The Crowd (1928)</t>
         </is>
       </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>The Crowd</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>The Crowd</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>King Vidor</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Eleanor Boardman, James Murray, Bert Roach</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>The life of a man and woman together in a large, impersonal metropolis through their hopes, struggles, and downfalls.</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZmRkNjk1ZDgtOTk2Ny00ZjU5LTg4NWQtYzNmNzFkMzA4MWMxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -8432,6 +11292,61 @@
           <t>G:\Archive\10231The Hard Way (1991)</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>The Hard Way</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>The Hard Way</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>John Badham</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Michael J. Fox, James Woods, Stephen Lang</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Action, Comedy, Crime</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>An action movie star researching a role is allowed to tag along with a hardboiled New York City policeman, who finds him superficial and irritating.</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BN2RkM2Y3MTAtZmZjYy00ZDUzLWE3OTMtZDgyODgyM2VhM2UzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -8460,6 +11375,61 @@
           <t>G:\Archive\10232The Shawshank Redemption (1994)</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>The Shawshank Redemption</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>The Shawshank Redemption</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Frank Darabont</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Tim Robbins, Morgan Freeman, Bob Gunton</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>A wrongfully convicted banker forms a close friendship with a hardened convict over a quarter century while retaining his humanity through simple acts of compassion.</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDAyY2FhYjctNDc5OS00MDNlLThiMGUtY2UxYWVkNGY2ZjljXkEyXkFqcGc@._V1_QL75_UX380_CR0,4,380,562_.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8488,6 +11458,61 @@
           <t>G:\Archive\10233The Sinners of Hell (1960)</t>
         </is>
       </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>The Sinners of Hell</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>The Sinners of Hell</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Nobuo Nakagawa</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Shigeru Amachi, Utako Mitsuya, Yôichi Numata</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>1960</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Crime, Drama, Horror</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>A group of sinners involved in interconnected tales of murder, revenge, deceit and adultery all meet at the Gates of Hell.</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BY2I5Mzk1MzMtNGRhZC00ZDkwLTlhMzQtNzIxNTQ1MjRjYmZiXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8516,6 +11541,61 @@
           <t>G:\Archive\10234Werckmeister Harmonies 2000</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Werckmeister Harmonies</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Werckmeister Harmonies</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Béla Tarr, Ágnes Hranitzky</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Lars Rudolph, Peter Fitz, Hanna Schygulla</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Drama, Mystery</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Hungary, Italy, Germany, France</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>A naive young man witnesses an escalation of violence in his small hometown following the arrival of a mysterious circus attraction.</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTdlOWFlMjYtOWFlNy00Nzk5LTljZDAtMDBmYTNjMWIxZTRmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -8544,6 +11624,61 @@
           <t>G:\Archive\10235Wild Mountain Thyme (2020)</t>
         </is>
       </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Wild Mountain Thyme</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Wild Mountain Thyme</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>John Patrick Shanley</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Emily Blunt, Jamie Dornan, Jon Hamm</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Comedy, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>United States, Ireland, United Kingdom</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>A pair of star-crossed lovers in Ireland get caught up in their family's land dispute.</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDc1NjcxMjEtMjU1Yy00MGY4LThjNzgtZTUyZDA5NWQ2ZGIwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -8572,6 +11707,61 @@
           <t>G:\Archive\10236Zatoichi and the Doomed Man (1965)</t>
         </is>
       </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Zatoichi and the Doomed Man</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Zatoichi and the Doomed Man</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Kazuo Mori</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Shintarô Katsu, Kanbi Fujiyama, Eiko Takashiro</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>The blind masseur and swordsman, Zatoichi, searches for proof an imprisoned man's innocence.</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNTc4OGRmZmQtN2U4Ny00MzkzLWExNDEtMWIwYmQ1ZTk2NTg0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -8600,6 +11790,61 @@
           <t>G:\Archive\10237Army of One (2020)</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Army of One</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Army of One</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Larry Charles</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Nicolas Cage, Russell Brand, Wendi McLendon-Covey</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Biography, Comedy, Crime</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Australia, United States</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>After a personal visit by God himself, the eccentric construction worker Gary Faulkner takes the decision to embark on an adventure in the badlands of Pakistan to bring Al-Qaeda's leader Osama Bin Laden to justice.</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYzNiZjFlYzQtMzc4YS00OGRkLWI3MTktYTg3MDZjYjE5ODNkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -8628,6 +11873,61 @@
           <t>G:\Archive\10238Black Dog (1998)</t>
         </is>
       </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Black Dog</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Black Dog</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Kevin Hooks</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Patrick Swayze, Randy Travis, Meat Loaf</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Action, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>United Kingdom, France, Germany, Japan, United States</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>A weapons loaded truck is shadowed by FBI and ATF. It explodes and kills the driver. Jack, just out of prison, is pressured into driving another truck from Atlanta to NJ. Things get rough when hijacking attempts are made.</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYWYzOTRlNDEtZmNmZC00YjFhLTg0MTctNGZhMzRmMDZiMjBlXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8656,6 +11956,61 @@
           <t>G:\Archive\10239Black River (1957)</t>
         </is>
       </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Black River</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Black River</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Jeff Bleckner</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Jay Mohr, Lisa Edelstein, Ann Cusack</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Mystery, Sci-Fi</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>A writer visits a town that isn't what it appears to be.</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTIxOTA0NDQ4N15BMl5BanBnXkFtZTcwNDcxNTAzMQ@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8684,6 +12039,61 @@
           <t>G:\Archive\10240Fire Will Come (2019)</t>
         </is>
       </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Fire Will Come</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Fire Will Come</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Óliver Laxe</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Amador Arias, Benedicta Sánchez, Inazio Abrao</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Spain, France, Luxembourg</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Amador returns home to his aging mother after serving a sentence for arson. He tries to adapt to daily farm life and coping with the villagers' memories of his past actions.</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjNmNjFlYTAtMzY5YS00OGYyLWEyZTMtODJkY2E0Y2Y3OWI4XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -8740,6 +12150,61 @@
           <t>G:\Archive\10242On Top of the Whale (1982)</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>On Top of the Whale</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>On Top of the Whale</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Raúl Ruiz</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Willeke van Ammelrooy, Jean Badin, Fernando Bordeu</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Fantasy, Mystery</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>A parody of anthropology, linguistics, and cultural imperialism. The film follows an unlikely team of linguists into the wilds of an ersatz Patagonia to study the last speakers of a dying language. That language apparently consist...</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjI1YThkYTQtY2MzYS00NDE1LTg2ZTItYzc4NTQyMmEzMjA2XkEyXkFqcGdeQXVyNDUxNjc5NjY@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8768,6 +12233,61 @@
           <t>G:\Archive\10243One Good Cop (1991)</t>
         </is>
       </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>One Good Cop</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>One Good Cop</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Heywood Gould</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Michael Keaton, Rene Russo, Anthony LaPaglia</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Action, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>An NYPD Detective (Michael Keaton) and his struggle for justice, while taking care of his late partner's three little girls after he is killed in the line of duty.</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTY1ZGI4YjEtY2E3Mi00ZTU4LWJmY2ItYjcwNGEwYzZlMTc3XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -8824,6 +12344,61 @@
           <t>G:\Archive\10245Redes (1936)</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Redes</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Redes</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Emilio Gómez Muriel, Fred Zinnemann</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Silvio Hernández, David Valle González, Rafael Hinojosa</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>A story of burgeoning labor rights amongst poor fishermen in a small village in Mexico.</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZWEyZmUzMmMtOTEzMy00ZTQ0LTgyMDktNDU3YjYwMzU2MzRiXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8852,6 +12427,61 @@
           <t>G:\Archive\10246She Devil (1989)</t>
         </is>
       </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>She Devil</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>She Devil</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Kurt Neumann</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Mari Blanchard, Jack Kelly, Albert Dekker</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Crime, Horror, Sci-Fi</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Doctors Scott and Bach inject the dying Kyra Zelas with a formula which saves her life - but also renders her almost immortal and wickedly evil.</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNDUyMjI0MGItODgyOC00MWM5LTkyMTEtYTk0MzhmOWIxNWMzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -8880,6 +12510,61 @@
           <t>G:\Archive\10247Someone to Watch over Me (1987)</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Someone to Watch Over Me</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Someone to Watch Over Me</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Ridley Scott</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Tom Berenger, Mimi Rogers, Lorraine Bracco</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Crime, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>A married New York cop falls for the socialite murder witness he's been assigned to protect.</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BN2FlOTBkYTktODllYS00NmVmLWI4ZjktNmU5YWM0MDc4YmFhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -8908,6 +12593,61 @@
           <t>G:\Archive\10248Switch (1991)</t>
         </is>
       </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Blake Edwards</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Ellen Barkin, Jimmy Smits, JoBeth Williams</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Comedy, Fantasy</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>A sexist womanizer is killed by one of his former lovers and then reincarnated as a woman.</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BM2NiNWVmZDctYTFjYS00MjQxLWFiMjgtMGE3ZjQ3ZTRiYjkwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -8936,6 +12676,61 @@
           <t>G:\Archive\10249Taipei Story (1985)</t>
         </is>
       </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Taipei Story</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Taipei Story</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Edward Yang</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Chin Tsai, Hsiao-Hsien Hou, I-Chen Ko</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>7.6</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Lung is a former member of the national Little League team who lives with his old childhood sweetheart Ah-chin, a traditional family woman. Although they live together, Ah-chin is weary of Lung's past liaison with another girl.</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMzE0MTdhOTgtMjVhYi00Yjk0LTkyZDAtN2M3MzAzNzQwYzU0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -8964,6 +12759,61 @@
           <t>G:\Archive\10250We Still Kill the Old Way (1967)</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>We Still Kill the Old Way</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>We Still Kill the Old Way</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Sacha Bennett</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Ian Ogilvy, Alison Doody, Danny Hatchard</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Action, Comedy, Crime</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>When retired East End villain Charlie Archer is murdered by a feral street gang, his brother Ritchie returns to London from Spain to investigate.</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDUzZmIyZTMtYWQxYi00YTk1LWIwZDctNzYxZjg3ZWVjOTIwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -8992,6 +12842,61 @@
           <t>G:\Archive\10251Ach du lieber Harry 1981</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Ach du lieber Harry</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Ach du lieber Harry</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Jean Girault</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Dieter Hallervorden, Iris Berben, Jacques Marin</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>West Germany</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Harry App is a private detective with only one goal: bring the priceless rabbit Mister Theo alive and well to Switzerland.</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTAxMjE2MzM0MjleQTJeQWpwZ15BbWU3MDE2NjI4MTE@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -9083,6 +12988,61 @@
           <t>G:\Archive\10253No Blade of Grass 1970</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>No Blade of Grass</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>No Blade of Grass</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Cornel Wilde</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Nigel Davenport, Jean Wallace, John Hamill</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Drama, Sci-Fi</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>United Kingdom, United States</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>An environmental catastrophe destroys civilization. Led by father John and mother Ann, the Custance clan sets out on a quest for safety in a savage world that may just end up turning them into the very thing they are fleeing.</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTg2NzBjNzctYWZhOC00Mjg4LWExYjYtYTQyNTdhZWQ4NmFkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -9111,6 +13071,61 @@
           <t>G:\Archive\10254Posse 1975</t>
         </is>
       </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Posse</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Posse</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Kirk Douglas</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Kirk Douglas, Bruce Dern, Bo Hopkins</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>An unscrupulous politico marshal and his deputies chase a gang of train robbers whose leader proves that every man has his price.</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNDc2NDJhNjQtZjc2OC00MzdmLWI0MjgtNmVkOTdjYjQyNGEwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -9139,6 +13154,61 @@
           <t>G:\Archive\10255Prancer 1989</t>
         </is>
       </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Prancer</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Prancer</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>John D. Hancock</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Sam Elliott, Cloris Leachman, Rutanya Alda</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Drama, Family, Fantasy</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>United States, Canada</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>A farm girl nurses a wounded reindeer she believes is one of Santa's, hoping to bring it back to health in time for Christmas. Her holiday spirit inspires those around her, something her disheartened father is having trouble under...</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjA1YmY4NGItZThlOS00M2IyLWE1ODAtMTQ4YTgxMTQ2ZmMyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -9167,6 +13237,61 @@
           <t>G:\Archive\10256The Catamount Killing 1974</t>
         </is>
       </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>The Catamount Killing</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>The Catamount Killing</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Krzysztof Zanussi</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Horst Buchholz, Ann Wedgeworth, Chip Taylor</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Poland, West Germany, United States</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>A banker troubled by both business and personal problems is transferred to a small town. There he meets and seduces an older woman. Together, they decide to pull off a payroll holdup together.</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYmFmN2QzMzItZDdjOS00MTI2LWFiNzQtYWE2ODhiMzA2MzgwXkEyXkFqcGdeQXVyNTY4ODAxODI@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -9195,6 +13320,61 @@
           <t>G:\Archive\10257The Killer 1989</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>The Killer</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>The Killer</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>John Woo</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Chow Yun-Fat, Danny Lee, Sally Yeh</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Action, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>A disillusioned assassin accepts one last hit in hopes of using his earnings to restore the vision of a singer he accidentally blinded.</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjQyZDJhNTktYjZiZC00ODU4LTg5OTYtYjc2MzA2OGFjMzZmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9279,6 +13459,61 @@
           <t>G:\Archive\10260Career Opportunities (1991)</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Career Opportunities</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Career Opportunities</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Bryan Gordon</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Frank Whaley, Jennifer Connelly, Dermot Mulroney</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Comedy, Romance</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Jim is the dorky son of a local cement contractor who lives at home and has no direction. Josie is the gorgeous daughter of a wealthy businessman who dreams of leaving town. They find they have a lot in common.</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjIyYmFhMDItNzdkOC00M2ZiLWI0MTAtZDhjZGUyMjBmN2QzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -9307,6 +13542,61 @@
           <t>G:\Archive\10261Great Expectations (1998)</t>
         </is>
       </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Great Expectations</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Great Expectations</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Alfonso Cuarón</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Ethan Hawke, Gwyneth Paltrow, Hank Azaria</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Modernization of Charles Dickens' classic story finds the hapless Finn as a painter in New York City pursuing his unrequited and haughty childhood love.</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjY2MTVhYmQtNDk0MS00MjFjLTkwNjItYzJhMjFiODllYzk1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -9335,6 +13625,61 @@
           <t>G:\Archive\10262Jungleland (2019)</t>
         </is>
       </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Jungleland</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Jungleland</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Max Winkler</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Charlie Hunnam, Jack O'Connell, Naheem Garcia</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>United Kingdom, United States</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Two brothers try to escape their circumstances by travelling across the country for a no holds barred boxing match that becomes a fight for their lives.</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMGRiYmVjNjUtMDliZS00NzkyLWJlOTEtNWQ3MWY5ZDMxMmRjXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -9419,6 +13764,61 @@
           <t>G:\Archive\10265Soul (2020)</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Soul</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Pete Docter, Kemp Powers</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Jamie Foxx, Tina Fey, Graham Norton</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Comedy</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Joe is a middle-school band teacher whose life hasn't quite gone the way he expected. His true passion is jazz. But when he travels to another realm to help someone find their passion, he soon discovers what it means to have soul.</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTZkYjA5MDEtMjY1ZC00ODk5LThjOTUtZDYxODEzYWNjMTU2XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -9447,6 +13847,61 @@
           <t>G:\Archive\10266The Croods A New Age (2020)</t>
         </is>
       </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>The Croods: A New Age</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>The Croods: A New Age</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Joel Crawford</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Nicolas Cage, Emma Stone, Ryan Reynolds</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Animation, Adventure, Comedy</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>United States, Japan</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>The prehistoric family the Croods are challenged by a rival family the Bettermans, who claim to be better and more evolved.</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTI1OTFhYmQtMzM4NS00Y2NkLTlkMmEtNTJhMWU1YWI0ZGQ2XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -9475,6 +13930,61 @@
           <t>G:\Archive\10267The Elephant Queen (2018)</t>
         </is>
       </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>The Elephant Queen</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>The Elephant Queen</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Mark Deeble, Victoria Stone</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Chiwetel Ejiofor</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Documentary, Family</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Athena is a mother who will do everything in her power to protect her herd when they are forced to leave their waterhole. This epic journey, narrated by Chiwetel Ejiofor, takes audiences across the African savannah, and into the h...</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODA5ZmYyOTAtODRhYy00N2QwLTliZmEtYmY1YTg1ZGM5ZDAzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -9503,6 +14013,61 @@
           <t>G:\Archive\10268The Kid Detective (2020)</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>The Kid Detective</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>The Kid Detective</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Evan Morgan</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Kaitlyn Chalmers-Rizzato, Adam Brody, Kaleb Horn</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Comedy, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>A once-celebrated kid detective, now 32, continues to solve the same trivial mysteries between hangovers and bouts of self-pity; until a naive client brings him his first 'adult' case to find out who brutally murdered her boyfriend.</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODkzYjMxNTAtODQxNy00Yjg1LTk4OWItM2JmYTlkMmRkMzczXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -9531,6 +14096,61 @@
           <t>G:\Archive\10269The Midnight Sky (2020)</t>
         </is>
       </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>The Midnight Sky</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>The Midnight Sky</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>George Clooney</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>George Clooney, Felicity Jones, David Oyelowo</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Adventure, Drama, Sci-Fi</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>5.7</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>This post-apocalyptic tale follows Augustine, a lonely scientist in the Arctic, as he races to stop Sully and her fellow astronauts from returning home to a mysterious global catastrophe.</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTE2NzJiM2UtZGRiMy00M2Q2LWFmZTAtYmI0MzVmZThkYTFhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -9559,6 +14179,61 @@
           <t>G:\Archive\10270The New Mutants (2020)</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>The New Mutants</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>The New Mutants</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Josh Boone</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Maisie Williams, Anya Taylor-Joy, Charlie Heaton</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Action, Horror, Mystery</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Five young mutants, just discovering their abilities while held in a secret facility against their will, fight to escape their past sins and save themselves.</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZGVlMjBkYmMtZDhmYS00N2QyLWI2YTgtMDU2N2UwOWYzM2MxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -9587,6 +14262,61 @@
           <t>G:\Archive\10271The Place of No Words (2019)</t>
         </is>
       </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>The Place of No Words</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>The Place of No Words</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Mark Webber</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Mark Webber, Teresa Palmer, Bodhi Palmer</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Fantasy</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>"Where do we go when we die?" A question by three-year-old Bodhi Palmer sets a real family on an imaginative adventure that explores how we cope with dying and the love, laughter, and pain we can find within it.</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYWQxMjA4NTUtYTQyZS00NmM3LWE1MGUtMWZmY2RkM2Q0YTIwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -9615,6 +14345,61 @@
           <t>G:\Archive\10272The Specials (2019)</t>
         </is>
       </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>The Specials</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>The Specials</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Olivier Nakache, Éric Toledano</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Vincent Cassel, Reda Kateb, Hélène Vincent</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Comedy, Drama</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>France, Belgium</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>The story of two men, educators of children and adolescents with autism.</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMDkxZWY0MzQtZmRlMS00NjlhLWFjOTItMGVhNzhkOTZiZDI5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -9643,6 +14428,61 @@
           <t>G:\Archive\10273Wander (2020)</t>
         </is>
       </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Wander</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Wander</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>April Mullen</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Aaron Eckhart, Tommy Lee Jones, Katheryn Winnick</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Thriller</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Canada, United States</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Hired to investigate a suspicious death in the town of Wander, a paranoid private eye becomes convinced the case is linked to a conspiracy and a cover-up.</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYzY2NjczNDItMTQ2Zi00OWI1LTkxNzktYjBkZmMzMmU4NzM1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -9671,6 +14511,61 @@
           <t>G:\Archive\10274Wolfwalkers (2020)</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Wolfwalkers</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Wolfwalkers</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Tomm Moore, Ross Stewart</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Honor Kneafsey, Eva Whittaker, Sean Bean</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Animation, Action, Adventure</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Ireland, Luxembourg, France, China, United States</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>A young apprentice hunter and her father journey to Ireland to help wipe out the last wolf pack. But everything changes when she befriends a free-spirited girl from a mysterious tribe rumored to transform into wolves by night.</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYzg3MjBkYmYtZjZkZS00YWVkLTk3YjMtNDBlMTVmNDZkZDJhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -9699,6 +14594,61 @@
           <t>G:\Archive\10275Wonder Woman 1984 (2020)</t>
         </is>
       </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Wonder Woman</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Wonder Woman</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Patty Jenkins</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Gal Gadot, Chris Pine, Robin Wright</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Fantasy</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>United States, China, Hong Kong</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>When a pilot crashes and tells of conflict in the outside world, Diana, an Amazonian warrior in training, leaves home to fight a war, discovering her full powers and true destiny.</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjEzYmZkNjktODBmYi00NzNkLWIzMjItMjhkMWZiZTZlN2MwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -9727,6 +14677,61 @@
           <t>G:\Archive\10277Black Bear (2020)</t>
         </is>
       </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Black Bear</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Lawrence Michael Levine</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Aubrey Plaza, Christopher Abbott, Sarah Gadon</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>A filmmaker at a creative impasse seeks solace from her tumultuous past at a rural retreat, only to find that the woods summon her inner demons in intense and surprising ways.</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTBhYjZmMDEtN2IxMS00N2MwLWI4ZDItM2MxMDY5MjUzYjBlXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -9755,6 +14760,61 @@
           <t>G:\Archive\10279Close My Eyes (1991)</t>
         </is>
       </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Close My Eyes</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Close My Eyes</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Stephen Poliakoff</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Alan Rickman, Clive Owen, Saskia Reeves</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>An estranged brother and sister begin an intense sexual relationship, behind the curtain of their otherwise normal working-class lives.</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOGVlOWU4ZDItODlhYi00ZTZlLWE2ZWYtNWMzYjA2NmNlZDE5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -9783,6 +14843,61 @@
           <t>G:\Archive\10280Critical Thinking (2020)</t>
         </is>
       </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Critical Thinking</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Critical Thinking</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>John Leguizamo</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>John Leguizamo, Rachel Bay Jones, Michael Kenneth Williams</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>The true story of the Miami Jackson High School chess team which was the first inner city team to win the U.S. National Chess Championship.</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNWNlNTI2OGMtZmEwNi00ZjFjLTkzMTYtNTBiOTU3ZTI1NTNkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -9811,6 +14926,61 @@
           <t>G:\Archive\10281Death in the Garden (1956)</t>
         </is>
       </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Death in the Garden</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Death in the Garden</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Luis Buñuel</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Simone Signoret, Georges Marchal, Charles Vanel</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Adventure, Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>France, Mexico</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Adventurer Shark comes to a small village near a diamond-miners' camp, and local police arrest him, accusing him of having committed a bank robbery in a neighboring town. The police also confiscate the diamond mine for the state, ...</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjgxYzA3YzgtODMyOC00NmUyLTk3NjQtMWU2Yjg4YzI4ZmY4XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -9839,6 +15009,61 @@
           <t>G:\Archive\10282Diamonds for Breakfast (1968)</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Diamonds for Breakfast</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Diamonds for Breakfast</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Christopher Morahan</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Marcello Mastroianni, Rita Tushingham, Elaine Taylor</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Comedy, Crime</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>The rightful heir to the Russian Imperial Jewels recruits a ragtag team of female petty thieves and cat burglars to steal them from a British museum.</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjc0ZGM4YzMtNzM4MC00YjZiLWE5NWEtMTEwMmYxYmE4NjRjXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -9867,6 +15092,61 @@
           <t>G:\Archive\10283Dojoji Temple (1976)</t>
         </is>
       </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Dojoji Temple</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Dojoji Temple</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Kihachirô Kawamoto</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Animation, Short</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>A man who is on a pilgrimage spends the night with a woman. After they share a moment of passion, he runs away and she chases him.</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYjY1NDQ3OGUtM2EzOC00MTllLWJlZWYtMzFiNWRhZjM0ZTlhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -9895,6 +15175,61 @@
           <t>G:\Archive\10284Ecstasy of the Angels (1972)</t>
         </is>
       </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Ecstasy of the Angels</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Ecstasy of the Angels</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Kôji Wakamatsu</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Ken Yoshizawa, Rie Yokoyama, Yuki Aresa</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Action, Drama, Mystery</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>A revolutionary faction steals some hand bombs. While escaping, several soldiers are killed. The movement's highest authority deems October unfit and sends the leader of another faction to take the remaining bombs.</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjdjZTRkM2ItNDY4NS00MWU0LWJmMWEtMDQ4ZmRjYWM2ZTBhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -9923,6 +15258,61 @@
           <t>G:\Archive\10285Fat Man and Little Boy (1989)</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Fat Man and Little Boy</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Fat Man and Little Boy</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Roland Joffé</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Paul Newman, Dwight Schultz, Bonnie Bedelia</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Biography, Drama, History</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>United States, Mexico</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>This film reenacts the Manhattan Project, the secret WWII project, and the first atomic bombs designed, built, and tested in Los Alamos.</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjM1NGM2MjctZmMxMi00N2Q4LTgzYjktYzA0MDg4MGRlMDc4XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -9951,6 +15341,61 @@
           <t>G:\Archive\10286Filmworker (2017)</t>
         </is>
       </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Filmworker</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Filmworker</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Tony Zierra</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Leon Vitali, Ryan O'Neal, Brian Capron</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Documentary, Biography</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>A documentary about how English actor Leon Vitali came to work as an assistant to American filmmaker Stanley Kubrick for over 30 years.</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODNmOWViNjItMzkzYy00MDRjLWIxNTktMTVkYjExNDQwMGE1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -9979,6 +15424,61 @@
           <t>G:\Archive\10287Fort Apache the Bronx (1981)</t>
         </is>
       </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Fort Apache the Bronx</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Fort Apache the Bronx</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Daniel Petrie</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Paul Newman, Edward Asner, Ken Wahl</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>In New York City, South Bronx's main police precinct is nicknamed Fort Apache by its employees who feel like troopers surrounded by hostiles in a wild west isolated outpost.</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDM0YjcxMjMtNmZmNC00MGUzLTkwZTEtZmJhMjA5NGM2ZjdiXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -10007,6 +15507,61 @@
           <t>G:\Archive\10288Fort Graveyard (1965)</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Fort Graveyard</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Fort Graveyard</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Kihachi Okamoto</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Toshirô Mifune, Makoto Satô, Reiko Dan</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>1965</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Drama, Music, War</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>In 1945, Japanese Army Sergeant Kosugi and a platoon of young green recruits must retake and defend a fort occupied by the Chinese forces.</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTI0MmQ1NTEtNjJkZC00YjU4LWI4NjItNTI5YTg0Y2QxMDVkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -10035,6 +15590,61 @@
           <t>G:\Archive\10289Ginza Cosmetics (1951)</t>
         </is>
       </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Ginza Cosmetics</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Ginza Cosmetics</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Mikio Naruse</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Kinuyo Tanaka, Ranko Hanai, Yûji Hori</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>A few days in the life of a quiet geisha, single mother of a young, smart boy, in the lively Tokyo quarter of Ginza. A woman devoted to other people's needs, she will end by taking part herself in one of the many disguises of Ginza.</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYmQ1ZjNhZjEtMzlmZC00ODgxLWIzZjYtNGM4MTdmNzIyNzgxXkEyXkFqcGdeQXVyMjcxNjI4NTk@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -10063,6 +15673,61 @@
           <t>G:\Archive\10290Gonza the Spearman (1986)</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Gonza the Spearman</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Gonza the Spearman</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Masahiro Shinoda</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Hiromi Gô, Shima Iwashita, Shohei Hino</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>The tragic story of Gonza, a handsome ladies man, set in the Tokagawa Period, a time in which appearences are very important. Gonza competes with Bannojo for the honor to perform the tea ceremony to celebrate the birth of an heir ...</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMzgyZWY2MzctNDhmZS00ZmUwLWFjZjYtYjc1OWYyYzRmYTMxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -10091,6 +15756,61 @@
           <t>G:\Archive\10291La viaccia (1961)</t>
         </is>
       </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>La viaccia</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>La viaccia</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Mauro Bolognini</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Jean-Paul Belmondo, Claudia Cardinale, Pietro Germi</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Italy, France</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>The original Italian is La Viaccia (the name of the family farm which motivates the plot). The death of a wealthy patriarch in 1885 sets off an interfamily power struggle. Son Ferdinando buys out his other relatives in order to ga...</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMGU5YTBhOTQtMTVmOC00NTczLWEyN2YtZjZhNGExM2QwYzkxXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -10119,6 +15839,61 @@
           <t>G:\Archive\10292Leo the Last (1970)</t>
         </is>
       </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Leo the Last</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Leo the Last</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>John Boorman</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Marcello Mastroianni, Billie Whitelaw, Calvin Lockhart</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Drama, Comedy</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>A social satire about the last heir of a dethroned family of European monarchs whose plans to return to power through revolution become secondary after he becomes fascinated by the life of a poor London black girl and her boyfriend.</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTMzOWE2MGQtNTE2MC00ZjMwLTk0ZDItNmRkYmRmZDdhOTkyXkEyXkFqcGdeQXVyMTQxNzMzNDI@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -10230,6 +16005,61 @@
           <t>G:\Archive\10294Let Him Go (2020)</t>
         </is>
       </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Let Him Go</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Let Him Go</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Thomas Bezucha</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Diane Lane, Kevin Costner, Kayli Carter</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Crime, Drama, Thriller</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>A retired sheriff and his wife, grieving over the death of their son, set out to find their only grandson.</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYTRhMjVkZmEtYmYyNi00NGJkLTkzYmQtOWE0MGJjZjUyNmFmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -10258,6 +16088,61 @@
           <t>G:\Archive\10295Let Them All Talk (2020)</t>
         </is>
       </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Let Them All Talk</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Let Them All Talk</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Steven Soderbergh</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Meryl Streep, Gemma Chan, Dianne Wiest</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Comedy, Drama</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>A famous author goes on a cruise trip with her friends and nephew in an effort to find fun and happiness while she comes to terms with her troubled past.</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjY1MTY1YzktMjc0Zi00ZDU1LThiMGEtODFkZDc4YmIxODAyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -10286,6 +16171,61 @@
           <t>G:\Archive\10296Life in a Year (2020)</t>
         </is>
       </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Life in a Year</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Life in a Year</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Mitja Okorn</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Jaden Smith, Cara Delevingne, Cuba Gooding Jr.</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>The movie follows 17-year-old Daryn who finds out that his girlfriend is dying. He sets out to give her an entire life in the last year she has left.</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOTYxMjRhZWYtZTUyNi00Y2FhLTlmM2UtNjBjOTY3MWYwZjZhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -10314,6 +16254,61 @@
           <t>G:\Archive\10297Mosul (2019)</t>
         </is>
       </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Mosul</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Matthew Michael Carnahan</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Waleed Elgadi, Suhail Dabbach, Adam Bessa</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Action, Drama, Thriller</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>United States, Germany, Canada, United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>A police unit from Mosul fight to liberate the Iraqi city from thousands of ISIS militants.</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BOGM4N2E5NDAtMWZjNC00ZWNjLTk4YjgtYTU0OGVjM2JmZDc3XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -10342,6 +16337,61 @@
           <t>G:\Archive\10298Pickpocket (1998)</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Pickpocket</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Pickpocket</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Robert Bresson</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Martin LaSalle, Marika Green, Jean Pélégri</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Crime, Drama</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Michel passes the time by picking pockets, careful to never be caught despite being watched by the police. His friend Jacques may suspect, while both men may have their eyes on Jeanne, the pretty neighbor of Michel's ailing mother.</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDk3MzJjOGYtY2I0OC00OTM4LWI4MDAtYjg1OTIwMjRmMDk1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -10370,6 +16420,61 @@
           <t>G:\Archive\10299Sin (2019)</t>
         </is>
       </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sin</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Don Tjernagel</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Don Tjernagel, Bram Zwingli, Matt Lee Ingebritson</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Horror</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>2.6</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>An entity is terrorizing a small Midwest town. Ludlow Falls continues to descend into madness and death as more young women are driven insane. Sometimes small towns hide big secrets and a town's sin will be exposed.</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjNkZmRiNTAtODBmYS00MDlhLWJlNTktZGU4MGFjZDg0MDg0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -10426,6 +16531,61 @@
           <t>G:\Archive\10301Up Close And Personal (1996)</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Up close and personal</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Up close and personal</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Raa Marchant</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Raa Marchant</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Documentary, Short, Thriller</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjRhMmQ3M2MtM2JiZi00ZDdkLTk5ZjAtNDhlNDEyNTU0N2JkXkEyXkFqcGdeQXVyNjE5MTQyNDc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -10454,6 +16614,61 @@
           <t>G:\Archive\10302A Gunfight 1971</t>
         </is>
       </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>A Gunfight</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>A Gunfight</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Lamont Johnson</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Kirk Douglas, Johnny Cash, Jane Alexander</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>1971</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Drama, Romance, Western</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Two aging gunfighters in need of money come to an agreement to organize an actual showdown between them and sell tickets for it. The townsfolk is more than interested to see the "show".</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNTMzZWY0MjAtMjYyZi00NjlhLTllOTQtODZiYWYyMTg0YzUyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -10482,6 +16697,61 @@
           <t>G:\Archive\10303Alles im Eimer 1981</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Alles im Eimer</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Alles im Eimer</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Ralf Gregan</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Dieter Hallervorden, Rainer Brandt, Dirk Dautzenberg</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>West Germany</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMmQzYzA0MDYtZTk1Yy00OThhLTgxZTktODgwOTIxNmI3NDE5XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -10510,6 +16780,61 @@
           <t>G:\Archive\10304Bei mir liegen Sie richtig 1990</t>
         </is>
       </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Bei mir liegen Sie richtig</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Bei mir liegen Sie richtig</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Ulrich Stark</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Dieter Hallervorden, Rosel Zech, Ezard Haußmann</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>1990</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Willi Kritz earns his living as a night watchman and body scrubber at the East-German Institute of Pathology at the University Hospital Berlin. He has opened another source of income: He steals pathological exhibits and smuggles t...</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTU1MDgyNDY2Nl5BMl5BanBnXkFtZTcwMzQ3MjAxMw@@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -10538,6 +16863,61 @@
           <t>G:\Archive\10305Ben-Hur 1959</t>
         </is>
       </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Ben-Hur</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Ben-Hur</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>William Wyler</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Charlton Heston, Jack Hawkins, Stephen Boyd</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>A Jewish prince is betrayed and sent into slavery by a Roman friend in 1st-century Jerusalem, but it's not long before he regains his freedom and comes back for revenge.</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjg2M2E1YzYtOThmMC00NjAyLWI5MzgtMDEwOGFiODdlOGUzXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -10566,6 +16946,61 @@
           <t>G:\Archive\10306Down the Ancient Stairs 1975</t>
         </is>
       </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Down the Ancient Stairs</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Down the Ancient Stairs</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Mauro Bolognini</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Marcello Mastroianni, Françoise Fabian, Marthe Keller</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Italy, France</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>A mental hospital somewhere in Tuscany during the thirties. Far away from fascism, this closed world is rules over by Dr. Bonaccorsi, a passionate benevolent psychiatrist whose dream is to isolate the germ of madness. He is also a...</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYTBmNGQ4MjctOWZhOC00NzJmLThmMzctOGZkMGQ2MDRlN2U0XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -10594,6 +17029,61 @@
           <t>G:\Archive\10307Dressed to Kill 1946</t>
         </is>
       </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Dressed to Kill</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Dressed to Kill</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Roy William Neill</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Basil Rathbone, Nigel Bruce, Patricia Morison</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Crime, Drama, Mystery</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>6.8</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>A trio of music boxes contains the hidden secret to riches, and a group of criminals will kill for them. In Vibrant Color.</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYmEyOTZhNWQtNjM5Mi00YWEzLWE3ZWMtZWExYWY5MTI3MWU1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -10622,6 +17112,61 @@
           <t>G:\Archive\10308Fort Yuma 1955</t>
         </is>
       </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Fort Yuma</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Fort Yuma</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Lesley Selander</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Peter Graves, Joan Vohs, John Hudson</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>1955</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Western</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>A disgruntled settler kills an Apache chief at Fort Yuma, and the fort's commander knows that the chief's son, Manga Colorado, will seek revenge and go on the warpath.</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYzc3ZTQyOWMtNmNhZS00ZjlmLTllOTQtMGRjMDdhZGEyYjVhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -10733,6 +17278,61 @@
           <t>G:\Archive\10310Hunger 1966</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Hunger</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Hunger</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Henning Carlsen</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Per Oscarsson, Gunnel Lindblom, Birgitte Federspiel</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Biography, Drama</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>7.7</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Denmark, Norway, Sweden</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>In 1890, Pontus, the starving writer, wanders the streets of Christiania, in search of love and a chance to get his work published. All he meets is defeat and suffering while his sense of reality is withering. One moment his is de...</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BYmJlMWVlNmMtMDUwNC00YjE4LTk4ZjMtNzRhZDhiYzVmZDQ3XkEyXkFqcGdeQXVyMTAwNzIyMzAy._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -10817,6 +17417,61 @@
           <t>G:\Archive\10314The Green Room 1978</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>The Green Room</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>The Green Room</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>François Truffaut</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>François Truffaut, Nathalie Baye, Jean Dasté</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>A French little town, at the end of the twenties. Julien Davenne is a journalist whose wife Julie died a decade ago. He gathered in the green room all Julie's objects. When a fire destroys the room, he renovates a little chapel an...</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNGI3MzE1YmItZmFiZC00MWU5LTg4NWYtMzllNjY5OTI2OGY4XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -10845,6 +17500,61 @@
           <t>G:\Archive\10315The Testament of Dr. Mabuse 1933</t>
         </is>
       </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>The Testament of Dr. Mabuse</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>The Testament of Dr. Mabuse</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Fritz Lang</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Rudolf Klein-Rogge, Otto Wernicke, Thomy Bourdelle</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>1933</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Crime, Mystery, Thriller</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Germany, France</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>A criminal mastermind uses hypnosis to rule the rackets after death.</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMTdjMmZlNWEtM2M4Ni00ZTQwLWE0ZjctMTkxODU4ZDg0MjhkXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -10873,6 +17583,61 @@
           <t>G:\Archive\10316A California Christmas (2020)</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>A California Christmas</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>A California Christmas</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Shaun Paul Piccinino</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Lauren Swickard, Josh Swickard, Ali Afshar</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Comedy, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>With his carefree lifestyle on the line, a wealthy charmer poses as a ranch hand to get a hardworking farmer to sell her family's land before Christmas.</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BODQyZWU2ZGEtZGM4My00YWQ0LWEwN2MtYTMzYTVlNTc0ZmI1XkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -10901,6 +17666,61 @@
           <t>G:\Archive\10317Adam (2020)</t>
         </is>
       </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Max Mayer</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Hugh Dancy, Rose Byrne, Peter Gallagher</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Comedy, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Adam, a lonely man with Asperger's Syndrome, develops a relationship with his upstairs neighbor, Beth.</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNzk1MTQ2YmYtNjBlNS00ZTcwLTg1MWItNjcxMjk4MDQ0N2JmXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -10957,6 +17777,61 @@
           <t>G:\Archive\10319Big Brown Eyes (1936)</t>
         </is>
       </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Big Brown Eyes</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Big Brown Eyes</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Raoul Walsh</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Cary Grant, Joan Bennett, Walter Pidgeon</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Comedy, Crime, Mystery</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Sassy manicurist Eve Fallon is recruited as an even more brassy reporter and she helps police detective boyfriend Danny Barr break a jewel theft ring and solve the murder of a baby.</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZGM0ZTQ3MmMtMzQzNy00MTdkLWE1MzEtZjVjNDQxNWE2NGQyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -10985,6 +17860,61 @@
           <t>G:\Archive\10320Booksellers (2019)</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>The Booksellers</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>The Booksellers</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>D.W. Young</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Parker Posey, Fran Lebowitz, Gay Talese</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Documentary</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>A behind-the-scenes look at the New York rare book world.</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjg4MTI5MzAtNTA1Ny00YmY4LWJmMTQtYzgxNGQ2ZjQwN2YyXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -11013,6 +17943,61 @@
           <t>G:\Archive\10321Bulletproof</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Bulletproof</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Bulletproof</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Ernest R. Dickerson</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Damon Wayans, Adam Sandler, James Caan</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Action, Comedy, Crime</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>5.8</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Two criminals, Keats and Moses, end their friendship, when Keats turns out to be an undercover cop. Many years later, the two are forced to work together when Keats is assigned to protect Moses as a witness.</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjUzY2NhNTgtMTMxYS00ZjdiLWI0NTMtY2VmOTA1NmE4MjcwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -11041,6 +18026,61 @@
           <t>G:\Archive\10322Carrie (1952)</t>
         </is>
       </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Carrie</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Carrie</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Brian De Palma</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Sissy Spacek, Piper Laurie, Amy Irving</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Horror</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Carrie White, a shy, friendless teenage girl who is sheltered by her domineering, religious mother, unleashes her telekinetic powers after being humiliated by her classmates at her senior prom.</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNjMwMDVlZjYtMWRlZS00OTU1LTlmYTQtOGViNTdmYTE0ZjRlXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -11069,6 +18109,61 @@
           <t>G:\Archive\10323Exodus Gods and Kings (2014)</t>
         </is>
       </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Exodus: Gods and Kings</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Exodus: Gods and Kings</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Ridley Scott</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Christian Bale, Joel Edgerton, Ben Kingsley</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Action, Adventure, Drama</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>United Kingdom, Spain, United States</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>The defiant leader Moses rises up against Egyptian Pharaoh Ramses II, setting six hundred thousand slaves on a monumental journey of escape from Egypt and its terrifying cycle of deadly plagues.</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BMjI3MDY0NjkxNl5BMl5BanBnXkFtZTgwNTM3NTA0MzE@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -11097,6 +18192,61 @@
           <t>G:\Archive\10324Experiment in Terror (1962)</t>
         </is>
       </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Experiment in Terror</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Experiment in Terror</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Blake Edwards</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Glenn Ford, Lee Remick, Stefanie Powers</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Crime, Mystery, Thriller</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>A man with an asthmatic voice telephones and assaults clerk Kelly Sherwood at home and coerces her into helping him steal a large sum from her bank.</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZDY3ZjczNDEtMDg4Yy00N2UyLTg3MzctYTAxNTMwM2QzYTMwXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -11125,6 +18275,61 @@
           <t>G:\Archive\10325Flesh+Blood (1985)</t>
         </is>
       </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Flesh, Blood &amp; Censorship</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Flesh, Blood &amp; Censorship</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Elijah Drenner</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Pete Walker</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Documentary, Short</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -11153,6 +18358,61 @@
           <t>G:\Archive\10326Fortress 1992</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Fortress</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Stuart Gordon</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Christopher Lambert, Loryn Locklin, Kurtwood Smith</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Action, Crime, Sci-Fi</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>In a future, private underground prison/Fortress, the inmates are computer controlled with CCTV, dream readers and devices that can cause pain or death. John and his illegally pregnant wife are inside but want to escape before birth.</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZTc4MTRkMTktMTFhYi00MGQ1LTlkNDUtNDgxNjk0OTM5NzdhXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -11181,6 +18441,61 @@
           <t>G:\Archive\10327Girlfriends (1978)</t>
         </is>
       </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Girlfriends</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Girlfriends</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Tracee Ellis Ross, Golden Brooks, Persia White</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>2000–2008</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Comedy, Drama, Romance</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>7.4</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>A look at the lives, loves, and losses of four different women: Toni, Maya, Lynn, and Joan.</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BZjE3NmY2ZGUtNzQ4Mi00YWIyLTg2MDMtMzMwNDQ2ZTU3OGZiXkEyXkFqcGc@._V1_SX300.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -11235,6 +18550,61 @@
       <c r="F241" t="inlineStr">
         <is>
           <t>G:\Archive\10330Lost Kubrick The Unfinished Films of Stanley Kubrick (2007)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Lost Kubrick: The Unfinished Films of Stanley Kubrick</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Lost Kubrick: The Unfinished Films of Stanley Kubrick</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Gary Leva</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Malcolm McDowell, Jack Nicholson, Sydney Pollack, Jan Harlan</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Documentary, Short</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>He is considered by many the greatest film director the medium has ever known. Yet in a 45-year career, Stanley Kubrick's films number only a dozen. That he strove for perfection is well ...</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/M/MV5BNGU5ZmI1ZDYtMjJhYS00MjM0LWE3ZjktZmM1Y2RlN2E3ZGE4XkEyXkFqcGdeQXVyMTM3NzQ5NzQ@._V1_SX300.jpg</t>
         </is>
       </c>
     </row>
